--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="D2">
-        <v>186</v>
+        <v>273</v>
       </c>
       <c r="E2">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D3">
-        <v>180</v>
+        <v>338</v>
       </c>
       <c r="E3">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -453,13 +453,13 @@
         <v>84</v>
       </c>
       <c r="D3">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H3">
         <v>426</v>
